--- a/reports/pumpfun_trades_live.xlsx
+++ b/reports/pumpfun_trades_live.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,12 +45,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="6">
@@ -107,14 +107,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -132,6 +132,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -616,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -626,7 +629,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -646,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -656,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -679,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+296.8%</t>
+          <t>+145.1%</t>
         </is>
       </c>
     </row>
@@ -702,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -712,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>6.014570215</v>
+        <v>17.017789345</v>
       </c>
     </row>
     <row r="21">
@@ -722,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>3.014570215</v>
+        <v>6.017789345000001</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1290,8 +1293,608 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>eˣinu</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>EINU</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>+1.9%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>+27.9%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>1.01933149</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0.0193314899999999</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 11.1% (-13.2% from peak, tol=10%)</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>FinfaNokT15sYU5n4AYMuQRUgQ9wnQjPWFfDCf8xGKjo</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:03</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>PokeBalance</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>BALANCE</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>+64.2%</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>+142.4%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>1.642356322</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0.6423563219999999</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 80.5% (-25.5% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>GTksGpwVJzv6PbwHPaengti9YT7KQoMK5tbRvDmwpump</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:05</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>The Cloned Horse</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>CAPACIDAD1</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>+51.4%</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>+103.8%</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>1.514305168</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>0.5143051679999999</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 66.2% (-18.4% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>imejxMNPEPcoZpZFuwXtAKfuj2tviwFFqkXQzwbpump</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:16</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Capacidad 1</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>CAPACIDAD</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>+48.1%</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>+102.8%</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>1.480803557</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>0.480803557</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 62.4% (-19.9% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>98m8iLoCamQAgaoLWsaD2XGAFCMJagqnDeRoEaoXhYKU</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:20</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Clearing</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>+107.3%</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>+220.9%</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>2.073287668</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>1.073287668</v>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 129.1% (-28.6% from peak, tol=28%)</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>8RFy7nMdKPpsvCzpoLT1fR3gBWrckDhYZF8iv1UBpump</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:38</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:04:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>horse wif goggles</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>hwg</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>+4.8%</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>+37.1%</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>1.048185495</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.04818549500000002</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 14.2% (-16.7% from peak, tol=10%)</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>AkFbeg5SA8s5z1x3bNCDpDCnHWtTaMVkftnfpGEDpump</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:40</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:03:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>trump inu</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>+22.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>+65.1%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>1.226684658</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>0.2266846579999999</v>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 34.1% (-18.8% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>FWQ6dmki3rASG1JBvA6FziucLqCHxPr4QSjNYLGspump</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:03:39</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:03:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>OpenCode Jr</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>OPENCODEJR</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>3S4YJZqitRucV26iqfMBa7k7dqfWCa36Qb1dTz8bpump</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:03:43</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Collapse TEK</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>$CTEK</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>+5.2%</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0.998264772</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>-0.001735228000000033</v>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 5.2% after 30s</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>HqikjFnepQyU12U52hubYuHEMEDKYp2fPucjVaHFpump</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:04:20</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Wallet Test - Do Not Buy</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>NOBUY</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>2FPFzRZogJUpXAMwaBNVD4pcYPLj2pJbZq81MZBPweNw</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:04:54</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1302,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1316,80 +1919,116 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Coin</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>LP tokens locked %</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total liquidity USD</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Reasons</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>Top holder tokens</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>2026-10-15 22:00:47</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>First Responders Coin</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>FRC</t>
         </is>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>135.291892573446</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=13 &gt; 5</t>
         </is>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>GiUgf9yEPfQXhgCnX9pVvJgiQYbfUcPosg8uxMCSpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 22:02:32</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>trump inu</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=21 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>J8qtuZ84VbcHfXc9Kr6TG6J2UFmA3KEQkVUFRzmRaRRJ</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades_live.xlsx
+++ b/reports/pumpfun_trades_live.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,15 +37,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,17 +67,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,9 +113,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -138,9 +138,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+145.1%</t>
+          <t>+97.6%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>17.017789345</v>
+        <v>16.677741259</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>6.017789345000001</v>
+        <v>2.677741259000001</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,43 +851,63 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>LOFI</t>
+          <t>bum</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>LOFI</t>
+          <t>bum</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>+29.7%</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="10" t="inlineStr"/>
-      <c r="J2" s="10" t="inlineStr"/>
+      <c r="I2" s="12" t="n">
+        <v>1.006577783</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>0.006577783000000004</v>
+      </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog trailing-stop 9.6% (-15.5% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>EaCzZRVGhdBL9VsAwui7Wc8pSUqMz97Ht4PsWoLQpump</t>
+          <t>23tZw1ZMsRG2ZVWzBNWqFS8BCkNXcVyJcbt5ckakpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:41</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:13</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:16</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -895,79 +915,127 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Cash Cat</t>
+          <t>PuzunSync</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>BLACKIE</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
+          <t>PUZUN</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>-8.0%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="10" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr"/>
+      <c r="I3" s="12" t="n">
+        <v>0.919905873</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>-0.08009412699999996</v>
+      </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog dead-coin 0.1% after 30s</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>63AJe8VZuQ9JbQc6L1JAwFZLQmxEovihVJmL4ucnpump</t>
+          <t>BExLBBVqk4mVVyU1GMk8Y9ZK5k8hCAefpoPgocKppump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:49</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:22</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:52</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr"/>
-      <c r="C4" s="10" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Obsidian</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>OBSIDIAN</t>
+        </is>
+      </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>+10.6%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>+42.9%</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="10" t="inlineStr"/>
-      <c r="J4" s="10" t="inlineStr"/>
+      <c r="I4" s="12" t="n">
+        <v>1.106062846</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>0.1060628459999999</v>
+      </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 20.7% (-15.6% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>43ePcpnkHoE4yXhaq5e9uQTdxGqNrzwam1AhDqk9pump</t>
+          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:51</t>
-        </is>
-      </c>
-      <c r="N4" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:24</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:35</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -975,27 +1043,27 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>pocketcat</t>
+          <t>MSCI官网：经非营运公司</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>POCKETCAT</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+          <t>MSCI官网：</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>+1.1%</t>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>+107.0%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1007,29 +1075,29 @@
         <v>1</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>1.010934489</v>
+        <v>1.012053947</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>0.01093448900000005</v>
+        <v>0.01205394700000006</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 10.1% (locked +25%, peak +107%)</t>
+          <t>watchdog dead-coin 6.7% after 30s</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>2Fx6F4psVTuqpzcp81zG5pn3RLyvkoz3gwXSQCz9pump</t>
+          <t>EqTr7549SQmGsUGVpJtQFabvZdedcbjP1yxbvhj7ittv</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:06</t>
+          <t>2026-10-16 00:53:26</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:08</t>
+          <t>2026-10-16 00:53:56</t>
         </is>
       </c>
     </row>
@@ -1039,43 +1107,63 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Babycat</t>
+          <t>NOSTRATEGY</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>BABYCAT</t>
+          <t>NSTR</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>+74.3%</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>+161.0%</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
+      <c r="I6" s="12" t="n">
+        <v>1.743007023</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>0.7430070230000001</v>
+      </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event ratchet-floor 91.8% (locked +100%, peak +161%)</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>FoiiMVPov1h5gkRAr6sQPbu6EvdMYc5bwpsURJ5ipump</t>
+          <t>8VgfKMmCYA3JxnzFD876Up9Rsiesf6zcmYPxiotdpump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:13</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:27</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1083,43 +1171,63 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>TRUMP INU</t>
+          <t>krrby</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>TRAMPINU</t>
+          <t>krrby</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>+20.0%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+61.5%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="I7" s="12" t="n">
+        <v>1.19970834</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.1997083399999999</v>
+      </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 31.1% (-18.8% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>yz9Fc1JnHRcgE8YefyqENsd2YcuX6yjonroVY58pump</t>
+          <t>krrb2QFwEQSYYvKGpEizwS63p5S5EMcUoS5UT812rjt</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:16</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:30</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:54:07</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -1127,27 +1235,27 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>niggi</t>
+          <t>OFFICIAL NEYMAR JR</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>niggi</t>
+          <t>NEYMAR</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>+51.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>+115.1%</t>
+          <t>+301.1%</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1159,29 +1267,29 @@
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1.518780008</v>
+        <v>0.9349975069999999</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.518780008</v>
+        <v>-0.06500249300000005</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 66.7% (-22.5% from peak, tol=18%)</t>
+          <t>trade-event ratchet-floor 1.7% (locked +100%, peak +301%)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>B4jL9bqN22dRU1s39Fk86ZzSMhD3Kmr2jLz7dLmGpump</t>
+          <t>A26Bz38Yag5uPM1EEbnBnSCMC1TrApNmuPQpddPnpump</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:28</t>
+          <t>2026-10-16 00:53:33</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:31</t>
+          <t>2026-10-16 00:53:48</t>
         </is>
       </c>
     </row>
@@ -1191,43 +1299,63 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>EPEPEˣ</t>
+          <t>MicroStrategy</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>EPEPE</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>+84.4%</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
+      <c r="I9" s="12" t="n">
+        <v>0.968298777</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>-0.031701223</v>
+      </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event ratchet-floor 5.4% (locked +25%, peak +84%)</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>cKkCAACEycRTxproR2cK1iVR4x3kqUQyoUZjNuq4yqP</t>
+          <t>7tm1TXFgaNRtFxU3rsfT2fSqDKMArmwFKMWftQr6pump</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:32</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr"/>
+          <t>2026-10-16 00:53:44</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:53:45</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -1235,63 +1363,43 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Lazarus</t>
+          <t>What Ipad</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>LAZARUS</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>+248.5%</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>+668.2%</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Ipad</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
       <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>3.484855718</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>2.484855718</v>
-      </c>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 290.5% (locked +350%, peak +668%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>GUDb9XpvotbogVH9V58QtnmUDV1SD6UByxy59T9Ppump</t>
+          <t>LpBSd8eFLUpTX8irA63Nrv2TUVDW2hmiPZQ6tyopump</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:01:35</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:01:35</t>
-        </is>
-      </c>
+          <t>2026-10-16 00:54:00</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1299,63 +1407,43 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>eˣinu</t>
+          <t>Trump $1 Coin Accelerationism</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>EINU</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>+1.9%</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>+27.9%</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>1/acc</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>1.01933149</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>0.0193314899999999</v>
-      </c>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 11.1% (-13.2% from peak, tol=10%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>FinfaNokT15sYU5n4AYMuQRUgQ9wnQjPWFfDCf8xGKjo</t>
+          <t>FYucNZjTiLrLcacyyqExmu3wGppDQ7EPKd8TLYyRpump</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:03</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:02:04</t>
-        </is>
-      </c>
+          <t>2026-10-16 00:54:27</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -1363,27 +1451,27 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>PokeBalance</t>
+          <t>TalkToMono</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>BALANCE</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
+          <t>MONO</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>+64.2%</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>+31.3%</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>+142.4%</t>
+          <t>+88.0%</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1395,29 +1483,29 @@
         <v>1</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1.642356322</v>
+        <v>1.313281777</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>0.6423563219999999</v>
+        <v>0.313281777</v>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 80.5% (-25.5% from peak, tol=18%)</t>
+          <t>watchdog trailing-stop 43.7% (-23.6% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>GTksGpwVJzv6PbwHPaengti9YT7KQoMK5tbRvDmwpump</t>
+          <t>2moYomAW5gvYr86UeeQWi45br1J6mt7yUxpnbxoApump</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:05</t>
+          <t>2026-10-16 00:54:37</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:07</t>
+          <t>2026-10-16 00:54:44</t>
         </is>
       </c>
     </row>
@@ -1427,27 +1515,27 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>The Cloned Horse</t>
+          <t>X Dollars</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>CAPACIDAD1</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+          <t>XUSD</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>+51.4%</t>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>+103.8%</t>
+          <t>+118.6%</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1459,29 +1547,29 @@
         <v>1</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>1.514305168</v>
+        <v>1.267351873</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>0.5143051679999999</v>
+        <v>0.267351873</v>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 66.2% (-18.4% from peak, tol=18%)</t>
+          <t>trade-event trailing-stop 38.6% (-36.6% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>imejxMNPEPcoZpZFuwXtAKfuj2tviwFFqkXQzwbpump</t>
+          <t>BXiL63aDT2vMzpVMcAUCUPSeGserqHhtrVfD8gTwpump</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:16</t>
+          <t>2026-10-16 00:55:04</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:18</t>
+          <t>2026-10-16 00:55:05</t>
         </is>
       </c>
     </row>
@@ -1491,27 +1579,27 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Capacidad 1</t>
+          <t>Goodest Barkley</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>CAPACIDAD</t>
+          <t>BARKLEY</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>+48.1%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>+102.8%</t>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1523,29 +1611,29 @@
         <v>1</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>1.480803557</v>
+        <v>0.946631384</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>0.480803557</v>
+        <v>-0.05336861599999998</v>
       </c>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 62.4% (-19.9% from peak, tol=18%)</t>
+          <t>watchdog dead-coin 3.0% after 30s</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>98m8iLoCamQAgaoLWsaD2XGAFCMJagqnDeRoEaoXhYKU</t>
+          <t>3WaWB7aswpNWptYVS7BwmkbyjHuR7N3KakGM69ANpump</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:20</t>
+          <t>2026-10-16 00:55:19</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:23</t>
+          <t>2026-10-16 00:55:49</t>
         </is>
       </c>
     </row>
@@ -1555,27 +1643,27 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Clearing</t>
+          <t>Chainmind</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>CLEAR</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+          <t>CHAIN</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>+107.3%</t>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+220.9%</t>
+          <t>+153.6%</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1587,29 +1675,29 @@
         <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>2.073287668</v>
+        <v>1.025323502</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>1.073287668</v>
+        <v>0.025323502</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 129.1% (-28.6% from peak, tol=28%)</t>
+          <t>watchdog ratchet-floor 11.7% (locked +100%, peak +154%)</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>8RFy7nMdKPpsvCzpoLT1fR3gBWrckDhYZF8iv1UBpump</t>
+          <t>4fSWwGMPCSttWJmrWCZPJGGX1N3yrSXWuLkonyDg4wkY</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:38</t>
+          <t>2026-10-16 00:55:20</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:04:17</t>
+          <t>2026-10-16 00:55:21</t>
         </is>
       </c>
     </row>
@@ -1619,63 +1707,43 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>horse wif goggles</t>
+          <t>Dog In Pain</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>hwg</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>+37.1%</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Dip</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>1.048185495</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>0.04818549500000002</v>
-      </c>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 14.2% (-16.7% from peak, tol=10%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>AkFbeg5SA8s5z1x3bNCDpDCnHWtTaMVkftnfpGEDpump</t>
+          <t>DMXzNXTuSgdJ4L1igjiSMRWsizAxhv6sg8F8zYp3pump</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:40</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:03:07</t>
-        </is>
-      </c>
+          <t>2026-10-16 00:55:56</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1683,63 +1751,43 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>trump inu</t>
+          <t>Save The Kids</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>TI</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>+22.7%</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>+65.1%</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>STK</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>1.226684658</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>0.2266846579999999</v>
-      </c>
+      <c r="I17" s="10" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr"/>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 34.1% (-18.8% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>FWQ6dmki3rASG1JBvA6FziucLqCHxPr4QSjNYLGspump</t>
+          <t>D8vFW9YMZtJ6nPejm5kmxdkNJnK4ho66diQYNMpDpump</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:03:39</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:03:41</t>
-        </is>
-      </c>
+          <t>2026-10-16 00:56:03</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -1747,20 +1795,20 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>OpenCode Jr</t>
+          <t>Rest In Property</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>OPENCODEJR</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+          <t xml:space="preserve">R.I.P </t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr"/>
+      <c r="E18" s="14" t="inlineStr"/>
       <c r="F18" s="9" t="inlineStr"/>
       <c r="G18" s="9" t="inlineStr"/>
       <c r="H18" s="12" t="n">
@@ -1775,12 +1823,12 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>3S4YJZqitRucV26iqfMBa7k7dqfWCa36Qb1dTz8bpump</t>
+          <t>6iU1VpG2xmJEf4SqerF94Ffm6T5b7515BB1x9iVVpump</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:03:43</t>
+          <t>2026-10-16 00:56:17</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr"/>
@@ -1791,27 +1839,27 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Collapse TEK</t>
+          <t>Save The Kids</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>$CTEK</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
+          <t>STK</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>+5.2%</t>
+          <t>+28.8%</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1823,29 +1871,29 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.998264772</v>
+        <v>1.039084354</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>-0.001735228000000033</v>
+        <v>0.0390843540000001</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 5.2% after 30s</t>
+          <t>trade-event trailing-stop 13.2% (-12.1% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>HqikjFnepQyU12U52hubYuHEMEDKYp2fPucjVaHFpump</t>
+          <t>HCcqt2gR96dYNSuuMB83Yo2CK6E9hkAVX8cRodEspump</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:04:20</t>
+          <t>2026-10-16 00:56:27</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15 22:04:50</t>
+          <t>2026-10-16 00:56:31</t>
         </is>
       </c>
     </row>
@@ -1855,46 +1903,198 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Wallet Test - Do Not Buy</t>
+          <t>Jewpad</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>NOBUY</t>
+          <t>JEWPAD</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr"/>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>+119.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>+277.9%</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="I20" s="12" t="n">
+        <v>2.195456273</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>1.195456273</v>
+      </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
+          <t>watchdog trailing-stop 142.9% (-35.7% from peak, tol=28%)</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>DSPEdQqHB8s54TxXrvwe1hP5DK2FmqyVn12r7opppump</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:28</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Save The Kids</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>STK</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr"/>
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>2FPFzRZogJUpXAMwaBNVD4pcYPLj2pJbZq81MZBPweNw</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-15 22:04:54</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>DYUuizMjaL4B57UKB3PpWVrBvPxv6ohX6zxpMaczpump</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:33</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Protect The Kids</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>PTK</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>CNpZFNMDWj2KmnPKoswASCN7fEZAfHCPjNswJ3Frpump</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:49</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Bomi Berzina</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>34d1ryy4YnJS2AoB836e5jHobuSvr5Vaay47VRWRpump</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:57:03</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1905,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1963,17 +2163,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 22:00:47</t>
+          <t>2026-10-16 00:53:15</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>First Responders Coin</t>
+          <t>Microducks</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>FRC</t>
+          <t>MICRODUCKS</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -1984,7 +2184,7 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=13 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
@@ -1992,24 +2192,24 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>GiUgf9yEPfQXhgCnX9pVvJgiQYbfUcPosg8uxMCSpump</t>
+          <t>FCUbf4HHAdGwrJpzmDT7PJfWWzuYqAyEwkGZLP6ypump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2026-10-15 22:02:32</t>
+          <t>2026-10-16 00:55:43</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>trump inu</t>
+          <t>Save The Kids</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>STK</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -2020,7 +2220,7 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=21 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=9 &gt; 5</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
@@ -2028,7 +2228,151 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>J8qtuZ84VbcHfXc9Kr6TG6J2UFmA3KEQkVUFRzmRaRRJ</t>
+          <t>7b7MTifXz3VCzUPUsBsnsQzvFUGGfYXyBbevh1qvpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:15</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Save the Children</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>STC</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=7 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>DXZDsKgUbzenV4rN9XyE4seMeU2CmioskUdeDP8Bpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:20</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Protect The Kids</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>PTK</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=13 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>84Gu7deoouCnNTDQALvc74uBL7QCy4HuePSjE12h3c5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:30</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Protect The Kids</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>PTK</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5; insider-whale 357,666,667 tokens (&gt;= 100,000,000)</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>357666666.666666</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>7uxZ67fXmZkPjxBMZYBwQaZtKqtbWah4vvvRTBjfpump</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 00:56:31</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Height Surgery</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>SIXFEET</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>64.6573620070609</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>1120.43539829464</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 64.66% | 2- Total Locked Liquidity $1.1K | BLOCK insider-whale 153,285,714 tokens (&gt;= 100,000,000); sniper-bundle 19 wallets besides LP</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>153285714.285713</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>4NaP5dGiYkAWsMCiJBn1qFADDMzSLhsra7B65VPBpump</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades_live.xlsx
+++ b/reports/pumpfun_trades_live.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,11 +37,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,9 +113,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -138,9 +138,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+97.6%</t>
+          <t>+72.5%</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>16.677741259</v>
+        <v>21.251472318</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2.677741259000001</v>
+        <v>5.251472318000001</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,61 +851,61 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>bum</t>
+          <t>SATINU</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>bum</t>
+          <t>SATINU</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>WON</t>
+          <t>LOST</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+29.7%</t>
+          <t>+108.9%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>1.006577783</v>
+        <v>0.979319382</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>0.006577783000000004</v>
+        <v>-0.02068061799999998</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 9.6% (-15.5% from peak, tol=10%)</t>
+          <t>watchdog breakeven -2.1%</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>23tZw1ZMsRG2ZVWzBNWqFS8BCkNXcVyJcbt5ckakpump</t>
+          <t>Cw3TfKqnvnsMGdYVm4kMFiowb2K5XXmR2vXYTxudpump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:13</t>
+          <t>2026-10-16 03:18:45</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:16</t>
+          <t>2026-10-16 03:18:46</t>
         </is>
       </c>
     </row>
@@ -915,27 +915,27 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>PuzunSync</t>
+          <t>do not wake it</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>PUZUN</t>
+          <t>w∅</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>LOST</t>
+          <t>WON</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>+41.2%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>+72.6%</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -947,29 +947,29 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>0.919905873</v>
+        <v>1.411799979</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>-0.08009412699999996</v>
+        <v>0.411799979</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 0.1% after 30s</t>
+          <t>trade-event trailing-stop 41.2% (-18.2% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>BExLBBVqk4mVVyU1GMk8Y9ZK5k8hCAefpoPgocKppump</t>
+          <t>32HoFP6Ne6RBkc635ZRVhSfx9YGWQomymATcdrGypump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:22</t>
+          <t>2026-10-16 03:19:24</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:52</t>
+          <t>2026-10-16 03:19:28</t>
         </is>
       </c>
     </row>
@@ -979,27 +979,27 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Obsidian</t>
+          <t>VICEPAD VI</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>OBSIDIAN</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+          <t>VP6</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>+10.6%</t>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>+42.9%</t>
+          <t>+86.2%</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -1011,29 +1011,29 @@
         <v>1</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1.106062846</v>
+        <v>1.344337891</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>0.1060628459999999</v>
+        <v>0.3443378909999999</v>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 20.7% (-15.6% from peak, tol=10%)</t>
+          <t>trade-event trailing-stop 34.4% (-27.8% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>4waSCsC6ppAxjAgVcLCiSVRX5L1Qv1zqTvAKkstkpump</t>
+          <t>FeYUHhfDoYzQ9kTvHxvSVTJkbnUKH6KcoWMTgERCpump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:24</t>
+          <t>2026-10-16 03:19:29</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:35</t>
+          <t>2026-10-16 03:19:30</t>
         </is>
       </c>
     </row>
@@ -1043,27 +1043,27 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>MSCI官网：经非营运公司</t>
+          <t>dx</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>MSCI官网：</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+          <t>dx</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>+1.2%</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>+6.8%</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1075,29 +1075,29 @@
         <v>1</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>1.012053947</v>
+        <v>1.068372408</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>0.01205394700000006</v>
+        <v>0.06837240800000011</v>
       </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 6.7% after 30s</t>
+          <t>watchdog dead-coin 7.9% after 30s</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>EqTr7549SQmGsUGVpJtQFabvZdedcbjP1yxbvhj7ittv</t>
+          <t>GZm9LXnjJE9zDjdfzSPvWoLKuGnQm3W9LvFiaofqpump</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:26</t>
+          <t>2026-10-16 03:19:56</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:56</t>
+          <t>2026-10-16 03:20:27</t>
         </is>
       </c>
     </row>
@@ -1107,63 +1107,43 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>NOSTRATEGY</t>
+          <t>Business Cat</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>NSTR</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>+74.3%</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>+161.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>BCAT</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>1.743007023</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>0.7430070230000001</v>
-      </c>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 91.8% (locked +100%, peak +161%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>8VgfKMmCYA3JxnzFD876Up9Rsiesf6zcmYPxiotdpump</t>
+          <t>4Gmj6FAZ8gLxReGHr3VqcnDL5qHqv7JjLDHR5B2gpump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:27</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:53:30</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:20:16</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -1171,63 +1151,43 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>krrby</t>
+          <t>Business Cat</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>krrby</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>+20.0%</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>+61.5%</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>BCAT</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="12" t="n">
-        <v>1.19970834</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>0.1997083399999999</v>
-      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 31.1% (-18.8% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>krrb2QFwEQSYYvKGpEizwS63p5S5EMcUoS5UT812rjt</t>
+          <t>68CiLfn5w7FNtBvkbDVA8uDymKFfDE8fU6C2fMBjpump</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:30</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:54:07</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:20:37</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -1235,27 +1195,27 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>OFFICIAL NEYMAR JR</t>
+          <t>Neural Networks Are Already</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>NEYMAR</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>LOST</t>
+          <t>WON</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>+64.5%</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>+301.1%</t>
+          <t>+101.8%</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1267,29 +1227,29 @@
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.9349975069999999</v>
+        <v>1.64544208</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>-0.06500249300000005</v>
+        <v>0.64544208</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 1.7% (locked +100%, peak +301%)</t>
+          <t>watchdog trailing-stop 64.5% (-18.5% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>A26Bz38Yag5uPM1EEbnBnSCMC1TrApNmuPQpddPnpump</t>
+          <t>3ttRNLsnk7CJwScgZbLLEuzSJ4GzmUHyLjvHYvztpump</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:33</t>
+          <t>2026-10-16 03:20:38</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:48</t>
+          <t>2026-10-16 03:20:46</t>
         </is>
       </c>
     </row>
@@ -1299,61 +1259,61 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>MicroStrategy</t>
+          <t>Browbera Thornhill</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+          <t>BROWBERA</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>-3.2%</t>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>+84.4%</t>
+          <t>+63.5%</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.968298777</v>
+        <v>0.939482669</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>-0.031701223</v>
+        <v>-0.06051733100000001</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 5.4% (locked +25%, peak +84%)</t>
+          <t>trade-event breakeven -6.1%</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>7tm1TXFgaNRtFxU3rsfT2fSqDKMArmwFKMWftQr6pump</t>
+          <t>7n1wrPswmFRmzbktqdcjTPo917SDjUCdEoeU2Q8Qpump</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:44</t>
+          <t>2026-10-16 03:20:49</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:45</t>
+          <t>2026-10-16 03:20:52</t>
         </is>
       </c>
     </row>
@@ -1363,43 +1323,63 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>What Ipad</t>
+          <t>farta</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Ipad</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
+          <t>farta</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>-14.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>-14.0%</t>
+        </is>
+      </c>
       <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
+      <c r="I10" s="12" t="n">
+        <v>0.860043054</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>-0.139956946</v>
+      </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog stop-loss -14.0%</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>LpBSd8eFLUpTX8irA63Nrv2TUVDW2hmiPZQ6tyopump</t>
+          <t>26vQuXrp4EwsCfpfDKhea9a3aSYcDFfLqEroQKUPpump</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:54:00</t>
-        </is>
-      </c>
-      <c r="N10" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:20:52</t>
+        </is>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:20:52</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1407,43 +1387,63 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Trump $1 Coin Accelerationism</t>
+          <t>yore</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>1/acc</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr"/>
+          <t>YORE</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>-7.3%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>-7.3%</t>
+        </is>
+      </c>
       <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
+      <c r="I11" s="12" t="n">
+        <v>0.9268142660000001</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>-0.07318573399999995</v>
+      </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog stop-loss -7.3%</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>FYucNZjTiLrLcacyyqExmu3wGppDQ7EPKd8TLYyRpump</t>
+          <t>2PSZFJhvftrKb6SAyBtEUUpFHXNnWZP4WQMeGW3Ryore</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:54:27</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:20:56</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:20:57</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -1451,63 +1451,43 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>TalkToMono</t>
+          <t>The Police Dog</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>MONO</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>+31.3%</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>+88.0%</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>1.313281777</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>0.313281777</v>
-      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 43.7% (-23.6% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>2moYomAW5gvYr86UeeQWi45br1J6mt7yUxpnbxoApump</t>
+          <t>tQn3jYX8xevg1frzbgCiSGNCLrdQZyL7QdpR1jqpump</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:54:37</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:54:44</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:20:59</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1515,27 +1495,27 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>X Dollars</t>
+          <t>mine-it</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>XUSD</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
+          <t>MINE</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>+26.7%</t>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>+191.1%</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>+118.6%</t>
+          <t>+307.1%</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1547,29 +1527,29 @@
         <v>1</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>1.267351873</v>
+        <v>2.910985471</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>0.267351873</v>
+        <v>1.910985471</v>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 38.6% (-36.6% from peak, tol=18%)</t>
+          <t>trade-event trailing-stop 191.1% (-28.5% from peak, tol=28%)</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>BXiL63aDT2vMzpVMcAUCUPSeGserqHhtrVfD8gTwpump</t>
+          <t>hX6AGedY845Cp87RiC2uw7ksLdbgcEwXe8yEiV6pump</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:04</t>
+          <t>2026-10-16 03:21:01</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:05</t>
+          <t>2026-10-16 03:21:05</t>
         </is>
       </c>
     </row>
@@ -1579,63 +1559,43 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Goodest Barkley</t>
+          <t>Afia Birago Frog</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>BARKLEY</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>-5.3%</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>+8.4%</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Afia</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>0.946631384</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>-0.05336861599999998</v>
-      </c>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 3.0% after 30s</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>3WaWB7aswpNWptYVS7BwmkbyjHuR7N3KakGM69ANpump</t>
+          <t>4kf2jNVQegciC2zME8ayMnAHVtS26jsxKKNjCqZmpump</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:19</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:55:49</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:21:13</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -1643,27 +1603,27 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Chainmind</t>
+          <t>rainforest</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>CHAIN</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+          <t>rainforest</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>WON</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>+2.5%</t>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>+22.5%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+153.6%</t>
+          <t>+39.4%</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
@@ -1675,29 +1635,29 @@
         <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>1.025323502</v>
+        <v>1.225302903</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>0.025323502</v>
+        <v>0.225302903</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>watchdog ratchet-floor 11.7% (locked +100%, peak +154%)</t>
+          <t>watchdog trailing-stop 22.5% (-12.1% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>4fSWwGMPCSttWJmrWCZPJGGX1N3yrSXWuLkonyDg4wkY</t>
+          <t>FVo6sJvTv7LfPiNrAExvHgke4cnKsnrzoKPyCujApump</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:20</t>
+          <t>2026-10-16 03:21:53</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:21</t>
+          <t>2026-10-16 03:21:56</t>
         </is>
       </c>
     </row>
@@ -1707,43 +1667,63 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Dog In Pain</t>
+          <t>Clawd</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Dip</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
+          <t>CLAWD</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>+17.1%</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>+53.1%</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
+      <c r="I16" s="12" t="n">
+        <v>1.170745033</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.170745033</v>
+      </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event ratchet-floor 17.1% (locked +25%, peak +53%)</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>DMXzNXTuSgdJ4L1igjiSMRWsizAxhv6sg8F8zYp3pump</t>
+          <t>BrxxteLyAfj29VcGWLchZJbtoVF6TWGL3NgSpLZapump</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:56</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:21:56</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:21:57</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1751,43 +1731,63 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Save The Kids</t>
+          <t>Catto</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
-      <c r="G17" s="9" t="inlineStr"/>
+          <t>CATTO</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>+0.3%</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
+      <c r="I17" s="12" t="n">
+        <v>0.993117934</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>-0.006882065999999964</v>
+      </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog dead-coin 0.3% after 30s</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>D8vFW9YMZtJ6nPejm5kmxdkNJnK4ho66diQYNMpDpump</t>
+          <t>72C7jmPzsYhd8fuZjSaf2e18joWpngQwo1WGu64Npump</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:03</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:21:57</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:22:27</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -1795,43 +1795,63 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Rest In Property</t>
+          <t>aura dog</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.I.P </t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr"/>
+          <t>auradog</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>+27.1%</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>+60.7%</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="10" t="inlineStr"/>
-      <c r="J18" s="10" t="inlineStr"/>
+      <c r="I18" s="12" t="n">
+        <v>1.270571733</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>0.2705717329999999</v>
+      </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 27.1% (-21.0% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>6iU1VpG2xmJEf4SqerF94Ffm6T5b7515BB1x9iVVpump</t>
+          <t>BocjhvTbZ4PVmu584mqfnFtbn9CkvTDNFjeRYio6pump</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:17</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:21:58</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:21:59</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -1839,63 +1859,43 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Save The Kids</t>
+          <t>Justice for Hermès</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>+3.9%</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>+28.8%</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>Hermès</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>1.039084354</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>0.0390843540000001</v>
-      </c>
+      <c r="I19" s="10" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr"/>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 13.2% (-12.1% from peak, tol=10%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>HCcqt2gR96dYNSuuMB83Yo2CK6E9hkAVX8cRodEspump</t>
+          <t>F7BibTme4rmvHrJbvw8ikTjkFBexjvEM3tczyDBGpump</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:27</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:56:31</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:22:09</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1903,63 +1903,43 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Jewpad</t>
+          <t>&lt;Privacy Pump&gt;</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>JEWPAD</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>+119.5%</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>+277.9%</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>&lt;P&gt;</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>2.195456273</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>1.195456273</v>
-      </c>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 142.9% (-35.7% from peak, tol=28%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>DSPEdQqHB8s54TxXrvwe1hP5DK2FmqyVn12r7opppump</t>
+          <t>6SyqC3EzudtZeAMx7eoHFxTMfyQkkzoT8kyjitkopump</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:28</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:56:32</t>
-        </is>
-      </c>
+          <t>2026-10-16 03:22:14</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -1967,43 +1947,63 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Save The Kids</t>
+          <t>PerpTide</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>STK</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="9" t="inlineStr"/>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>+48.2%</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>+81.3%</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="10" t="inlineStr"/>
+      <c r="I21" s="12" t="n">
+        <v>1.482309796</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>0.482309796</v>
+      </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 48.2% (-18.2% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>DYUuizMjaL4B57UKB3PpWVrBvPxv6ohX6zxpMaczpump</t>
+          <t>Dm9G7f6HtrtWX2SzCtWTkCLHpfP9phSpe4BVvDR9pump</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:33</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:22:19</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:22:20</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -2011,43 +2011,63 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Protect The Kids</t>
+          <t>Big Ugly Cucks</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>PTK</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
+          <t>BUC</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>+3.1%</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>+19.0%</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
+      <c r="I22" s="12" t="n">
+        <v>1.03090547</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>0.03090546999999999</v>
+      </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 3.1% (-13.4% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>CNpZFNMDWj2KmnPKoswASCN7fEZAfHCPjNswJ3Frpump</t>
+          <t>JANiakLq3CbkQmmkVsnwrExwEvonYN2x1tZySUtzpump</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:49</t>
-        </is>
-      </c>
-      <c r="N22" s="10" t="inlineStr"/>
+          <t>2026-10-16 03:22:23</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:22:47</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -2055,46 +2075,154 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Bomi Berzina</t>
+          <t>Big Ugly Cucks</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>BB</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
+          <t>BUC</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>+99.2%</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>+157.9%</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>1.991922249</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>0.9919222489999999</v>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>trade-event ratchet-floor 99.2% (locked +100%, peak +158%)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>J77Z9ACmdmKdNJ63LpufGqW8RpZyxh9jybPN5W9ypump</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:23:09</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AutoCorp</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>CORP</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>34d1ryy4YnJS2AoB836e5jHobuSvr5Vaay47VRWRpump</t>
-        </is>
-      </c>
-      <c r="M23" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:57:03</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="inlineStr"/>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>EkC97ruNmtDw9Rq3DPXTwhx6VhxTgrRH6m7XvsjAkKUM</t>
+        </is>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:23:41</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>number go hmm</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>PONDR</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>9EaQMq1EMbFZNHSdYwZuB5HCxEqfX6Dca2uSKhWnpump</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 03:23:59</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N23"/>
+  <autoFilter ref="A1:N25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2105,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2163,17 +2291,17 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:53:15</t>
+          <t>2026-10-16 03:20:08</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Microducks</t>
+          <t>50 Scent</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>MICRODUCKS</t>
+          <t>50 Scent</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
@@ -2184,7 +2312,7 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=12 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=27 &gt; 5</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
@@ -2192,132 +2320,132 @@
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>FCUbf4HHAdGwrJpzmDT7PJfWWzuYqAyEwkGZLP6ypump</t>
+          <t>29LArDCs37HMj3fgy7rh2xc9qUkc885QYNUykLAgpump</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:55:43</t>
+          <t>2026-10-16 03:20:50</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Save The Kids</t>
+          <t>Saindra</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>STK</t>
+          <t>SAINDRA</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>50.52363835772071</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0</v>
+        <v>1821.64592557876</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=9 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 50.52% | 2- Total Locked Liquidity $1.8K | BLOCK insider-whale 126,235,294 tokens (&gt;= 100,000,000); sniper-bundle 10 wallets besides LP</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0</v>
+        <v>126235294.117647</v>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>7b7MTifXz3VCzUPUsBsnsQzvFUGGfYXyBbevh1qvpump</t>
+          <t>7bQwGYwJzwcegyt8Ejyobu39BYLg5xFNuJka15Qypump</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:15</t>
+          <t>2026-10-16 03:20:54</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Save the Children</t>
+          <t>Doge4Goat</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>STC</t>
+          <t>Doge4Goat</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>54.83302030941268</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0</v>
+        <v>1583.46437885452</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=7 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 54.83% | 2- Total Locked Liquidity $1.6K | BLOCK sniper-bundle 19 wallets besides LP</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0</v>
+        <v>68971002.17336901</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>DXZDsKgUbzenV4rN9XyE4seMeU2CmioskUdeDP8Bpump</t>
+          <t>6nsnpCggMD3CPSstZXKCiFPTdRx72JZZzxyCz3prpump</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:20</t>
+          <t>2026-10-16 03:20:55</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Protect The Kids</t>
+          <t>CLAU</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>PTK</t>
+          <t>CLAU</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>99.53393542612206</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>0</v>
+        <v>10.92207442124</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=13 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 99.53% | 2- Total Locked Liquidity $11 | BLOCK sniper-bundle 14 wallets besides LP</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0</v>
+        <v>32712312.494382</v>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>84Gu7deoouCnNTDQALvc74uBL7QCy4HuePSjE12h3c5m</t>
+          <t>6iq5aCmEFh96XZswHgzivLn1XN4Y8N7aFioAGyMPpump</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 00:56:30</t>
+          <t>2026-10-16 03:22:22</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Protect The Kids</t>
+          <t>Afia Birago Frog</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>PTK</t>
+          <t>Afia</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -2328,51 +2456,15 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=6 &gt; 5; insider-whale 357,666,667 tokens (&gt;= 100,000,000)</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=37 &gt; 5</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>357666666.666666</v>
+        <v>0</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>7uxZ67fXmZkPjxBMZYBwQaZtKqtbWah4vvvRTBjfpump</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-16 00:56:31</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Height Surgery</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>SIXFEET</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>64.6573620070609</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>1120.43539829464</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 64.66% | 2- Total Locked Liquidity $1.1K | BLOCK insider-whale 153,285,714 tokens (&gt;= 100,000,000); sniper-bundle 19 wallets besides LP</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>153285714.285713</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>4NaP5dGiYkAWsMCiJBn1qFADDMzSLhsra7B65VPBpump</t>
+          <t>JNgK7oNeuJWS14Wxoj5MwPfGDiLK8zCL9jm2orcgrAS</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades_live.xlsx
+++ b/reports/pumpfun_trades_live.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+72.5%</t>
+          <t>+63.0%</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>21.251472318</v>
+        <v>28.080913787</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>5.251472318000001</v>
+        <v>6.080913787</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,12 +851,12 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>SATINU</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>SATINU</t>
+          <t>OKAY</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -866,46 +866,46 @@
       </c>
       <c r="E2" s="11" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>+108.9%</t>
+          <t>+76.9%</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>0.979319382</v>
+        <v>0.958761799</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>-0.02068061799999998</v>
+        <v>-0.04123820099999997</v>
       </c>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>watchdog breakeven -2.1%</t>
+          <t>trade-event breakeven -4.1%</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>Cw3TfKqnvnsMGdYVm4kMFiowb2K5XXmR2vXYTxudpump</t>
+          <t>GHnGviuMzqMoBx8NuZNN3X5QDkYA7mZBu3xVGoPNmVzT</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:18:45</t>
+          <t>2026-10-16 04:50:24</t>
         </is>
       </c>
       <c r="N2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:18:46</t>
+          <t>2026-10-16 04:50:25</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>do not wake it</t>
+          <t>Flying Tesla Roadster 2.0</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>w∅</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>+41.2%</t>
+          <t>+24.4%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>+72.6%</t>
+          <t>+68.5%</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -947,29 +947,29 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>1.411799979</v>
+        <v>1.244047792</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.411799979</v>
+        <v>0.2440477919999999</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 41.2% (-18.2% from peak, tol=18%)</t>
+          <t>trade-event ratchet-floor 24.4% (locked +25%, peak +68%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>32HoFP6Ne6RBkc635ZRVhSfx9YGWQomymATcdrGypump</t>
+          <t>J5s6eTHv3ZhzG5X4LrEwbr1LgRoj5tSmsZDrxntMpump</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:19:24</t>
+          <t>2026-10-16 04:50:29</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:19:28</t>
+          <t>2026-10-16 04:50:31</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>VICEPAD VI</t>
+          <t>numen.cash</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>VP6</t>
+          <t>NUMEN</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>+34.4%</t>
+          <t>+56.8%</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>+86.2%</t>
+          <t>+97.7%</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -1011,29 +1011,29 @@
         <v>1</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1.344337891</v>
+        <v>1.568295652</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>0.3443378909999999</v>
+        <v>0.568295652</v>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 34.4% (-27.8% from peak, tol=18%)</t>
+          <t>watchdog trailing-stop 56.8% (-20.7% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>FeYUHhfDoYzQ9kTvHxvSVTJkbnUKH6KcoWMTgERCpump</t>
+          <t>GvEjB2Z24Hbq3Tf3F5e5vPgBpmV5p7YnL4SLDpoapump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:19:29</t>
+          <t>2026-10-16 04:50:31</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:19:30</t>
+          <t>2026-10-16 04:50:47</t>
         </is>
       </c>
     </row>
@@ -1043,63 +1043,43 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>dx</t>
+          <t>p-null.si</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>dx</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>+6.8%</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>+7.9%</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>p(null)</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr"/>
       <c r="H5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="12" t="n">
-        <v>1.068372408</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>0.06837240800000011</v>
-      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 7.9% after 30s</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>GZm9LXnjJE9zDjdfzSPvWoLKuGnQm3W9LvFiaofqpump</t>
+          <t>DuQU1Fi4KmT4cQgn1k1QYkqtYVEMRhEXbdijsipypump</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:19:56</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 03:20:27</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:50:37</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1107,12 +1087,12 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Business Cat</t>
+          <t>Cuck Coding</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>BCAT</t>
+          <t>Cuck</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1135,12 +1115,12 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>4Gmj6FAZ8gLxReGHr3VqcnDL5qHqv7JjLDHR5B2gpump</t>
+          <t>4RrzBXWpbXbSsTNHxDxEjffrSzuG4HPoSLwPr7yVpump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:16</t>
+          <t>2026-10-16 04:50:41</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr"/>
@@ -1151,43 +1131,63 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Business Cat</t>
+          <t>Carcoin</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>BCAT</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
-      <c r="G7" s="9" t="inlineStr"/>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>+18.5%</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+44.3%</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
+      <c r="I7" s="12" t="n">
+        <v>1.184982451</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>0.184982451</v>
+      </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 18.5% (-17.9% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>68CiLfn5w7FNtBvkbDVA8uDymKFfDE8fU6C2fMBjpump</t>
+          <t>E8W7MLBp7anWDj1zS5FCtF4Xb2nehzT8ze7UDd91pump</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:37</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:50:42</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:50:43</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -1195,61 +1195,61 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Neural Networks Are Already</t>
+          <t>Flying Tesla Roadster 2.0</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>CLEAN</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>+64.5%</t>
+          <t>FTR2</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>+101.8%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>1.64544208</v>
+        <v>0.9245233430000001</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0.64544208</v>
+        <v>-0.07547665699999995</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 64.5% (-18.5% from peak, tol=18%)</t>
+          <t>trade-event stop-loss -7.5%</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>3ttRNLsnk7CJwScgZbLLEuzSJ4GzmUHyLjvHYvztpump</t>
+          <t>Ex8ZXJUp2WbmHJXmA1TfJkL8RVngbHBqTD7JDz1Xpump</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:38</t>
+          <t>2026-10-16 04:51:09</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:46</t>
+          <t>2026-10-16 04:51:10</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Browbera Thornhill</t>
+          <t>I Wish Tech Wasn't Here</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>BROWBERA</t>
+          <t>IWTH</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1274,46 +1274,46 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>+63.5%</t>
+          <t>+32.9%</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.939482669</v>
+        <v>0.924192439</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>-0.06051733100000001</v>
+        <v>-0.07580756099999997</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -6.1%</t>
+          <t>watchdog breakeven -7.6%</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>7n1wrPswmFRmzbktqdcjTPo917SDjUCdEoeU2Q8Qpump</t>
+          <t>FdnSb7PCMQTfJ1T2335YYdTyGrJhtKx79X9pgLRUpump</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:49</t>
+          <t>2026-10-16 04:51:31</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:52</t>
+          <t>2026-10-16 04:51:32</t>
         </is>
       </c>
     </row>
@@ -1323,61 +1323,61 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>farta</t>
+          <t>Tesla x SpaceX</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>farta</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>-14.0%</t>
+          <t>TESLAXSPX</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
+          <t>+8.5%</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>-14.0%</t>
-        </is>
-      </c>
       <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>0.860043054</v>
+        <v>1.073717595</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>-0.139956946</v>
+        <v>0.07371759499999997</v>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -14.0%</t>
+          <t>watchdog dead-coin 8.5% after 30s</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>26vQuXrp4EwsCfpfDKhea9a3aSYcDFfLqEroQKUPpump</t>
+          <t>CdpmUkhuiCArgH7LUUWVjU8LoQV3iZiYLpDAY79JxkiC</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:52</t>
+          <t>2026-10-16 04:51:40</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:52</t>
+          <t>2026-10-16 04:52:11</t>
         </is>
       </c>
     </row>
@@ -1387,61 +1387,61 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>yore</t>
+          <t>gently used  tesla roadster</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>YORE</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>-7.3%</t>
+          <t>UTR</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
+          <t>+24.5%</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>-7.3%</t>
-        </is>
-      </c>
       <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>0.9268142660000001</v>
+        <v>1.028018102</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>-0.07318573399999995</v>
+        <v>0.0280181020000001</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>watchdog stop-loss -7.3%</t>
+          <t>trade-event trailing-stop 2.8% (-17.4% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>2PSZFJhvftrKb6SAyBtEUUpFHXNnWZP4WQMeGW3Ryore</t>
+          <t>J6pEUdFLH72dAjLwxyc5Gjn9ukF6ERc6zpFSwdNTpump</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:56</t>
+          <t>2026-10-16 04:51:48</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:57</t>
+          <t>2026-10-16 04:51:49</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>The Police Dog</t>
+          <t>Flying Tesla Roadster</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Hermès</t>
+          <t>FTR</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>tQn3jYX8xevg1frzbgCiSGNCLrdQZyL7QdpR1jqpump</t>
+          <t>XUWauZnrx6oHSQyQosg88jwnM3gdVFqH4UZyjWDpump</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:59</t>
+          <t>2026-10-16 04:52:00</t>
         </is>
       </c>
       <c r="N12" s="10" t="inlineStr"/>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>mine-it</t>
+          <t>AgentPlay</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>AGENTPLAY</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>+191.1%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>+307.1%</t>
+          <t>+70.8%</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1527,29 +1527,29 @@
         <v>1</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>2.910985471</v>
+        <v>1.350549879</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>1.910985471</v>
+        <v>0.3505498789999999</v>
       </c>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 191.1% (-28.5% from peak, tol=28%)</t>
+          <t>trade-event trailing-stop 35.1% (-20.9% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>hX6AGedY845Cp87RiC2uw7ksLdbgcEwXe8yEiV6pump</t>
+          <t>ufPxxVUMKC1if3JFYuWSDiMSGbJtq9yRGVdprZUpump</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:01</t>
+          <t>2026-10-16 04:52:12</t>
         </is>
       </c>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:05</t>
+          <t>2026-10-16 04:52:13</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Afia Birago Frog</t>
+          <t>grokazon</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Afia</t>
+          <t>grokazon</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>4kf2jNVQegciC2zME8ayMnAHVtS26jsxKKNjCqZmpump</t>
+          <t>Ch7gZZqhZRnHnLJJsdpypNghGn3fDjuxQtr5qeWPpump</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:13</t>
+          <t>2026-10-16 04:52:15</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr"/>
@@ -1603,61 +1603,61 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>rainforest</t>
+          <t>Exploding Tesla Roadster</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>rainforest</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>+22.5%</t>
+          <t>ETR</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+39.4%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>1.225302903</v>
+        <v>0.956004272</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>0.225302903</v>
+        <v>-0.04399572799999996</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 22.5% (-12.1% from peak, tol=10%)</t>
+          <t>trade-event stop-loss -4.4%</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>FVo6sJvTv7LfPiNrAExvHgke4cnKsnrzoKPyCujApump</t>
+          <t>DLP9o7efJKwJfX5QJ9FDGYohoCj3s6v99QkLKzeYpump</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:53</t>
+          <t>2026-10-16 04:52:54</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:56</t>
+          <t>2026-10-16 04:52:54</t>
         </is>
       </c>
     </row>
@@ -1667,63 +1667,43 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Clawd</t>
+          <t>Sucking Tesla Roadster</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>CLAWD</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>+17.1%</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>+53.1%</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>1.170745033</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>0.170745033</v>
-      </c>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 17.1% (locked +25%, peak +53%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>BrxxteLyAfj29VcGWLchZJbtoVF6TWGL3NgSpLZapump</t>
+          <t>AHnrPnY2pt7TCHXCS6CVd8d5pze4Nn59e16tJDYHpump</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:56</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 03:21:57</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:52:59</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1731,27 +1711,27 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Catto</t>
+          <t>Slighty Used Tesla Roadstar</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>CATTO</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
+          <t>Roadstar</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>+8.4%</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -1763,29 +1743,29 @@
         <v>1</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0.993117934</v>
+        <v>1.084297394</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>-0.006882065999999964</v>
+        <v>0.08429739400000003</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 0.3% after 30s</t>
+          <t>watchdog dead-coin 9.5% after 30s</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>72C7jmPzsYhd8fuZjSaf2e18joWpngQwo1WGu64Npump</t>
+          <t>5psJDSu949XhzPQdfsvoGvF5kbLC3TjsQWpMdSw1pump</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:57</t>
+          <t>2026-10-16 04:53:06</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:27</t>
+          <t>2026-10-16 04:53:36</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1775,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>aura dog</t>
+          <t>Tesla Roadster</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>auradog</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -1810,12 +1790,12 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>+27.1%</t>
+          <t>+17.7%</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>+60.7%</t>
+          <t>+40.3%</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1827,29 +1807,29 @@
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1.270571733</v>
+        <v>1.17672305</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>0.2705717329999999</v>
+        <v>0.1767230500000001</v>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 27.1% (-21.0% from peak, tol=18%)</t>
+          <t>trade-event trailing-stop 17.7% (-16.1% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>BocjhvTbZ4PVmu584mqfnFtbn9CkvTDNFjeRYio6pump</t>
+          <t>18vuF9YNerpXUcSKBMLH7nqmxAiwe6FJCxRJeAopump</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:58</t>
+          <t>2026-10-16 04:53:09</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:21:59</t>
+          <t>2026-10-16 04:53:12</t>
         </is>
       </c>
     </row>
@@ -1859,43 +1839,63 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Justice for Hermès</t>
+          <t>Claudia's Cat Clay</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Hermès</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="9" t="inlineStr"/>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>+32.7%</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>+76.3%</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="10" t="inlineStr"/>
+      <c r="I19" s="12" t="n">
+        <v>1.326804239</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0.3268042390000001</v>
+      </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 32.7% (-24.8% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>F7BibTme4rmvHrJbvw8ikTjkFBexjvEM3tczyDBGpump</t>
+          <t>HLLwUbjfueZo1jw5fSML6MDbg9YzbCPGT8qcjJjfpump</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:09</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:53:15</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:53:16</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -1903,43 +1903,63 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>&lt;Privacy Pump&gt;</t>
+          <t>Underrated Profit Simulator</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>&lt;P&gt;</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr"/>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>+70.3%</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>+108.0%</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="10" t="inlineStr"/>
+      <c r="I20" s="12" t="n">
+        <v>1.70306778</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0.70306778</v>
+      </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 70.3% (-18.1% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>6SyqC3EzudtZeAMx7eoHFxTMfyQkkzoT8kyjitkopump</t>
+          <t>E9Xiz6zzpiBsMDkMMpHjnb2bfxvZWAKK1vk4cpV6pump</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:14</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:53:21</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:53:35</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -1947,12 +1967,12 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>PerpTide</t>
+          <t>Tesla Roadster</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Roadster</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -1962,12 +1982,12 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>+48.2%</t>
+          <t>+28.9%</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>+81.3%</t>
+          <t>+82.6%</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1979,29 +1999,29 @@
         <v>1</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>1.482309796</v>
+        <v>1.288676328</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>0.482309796</v>
+        <v>0.288676328</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 48.2% (-18.2% from peak, tol=18%)</t>
+          <t>trade-event trailing-stop 28.9% (-29.4% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Dm9G7f6HtrtWX2SzCtWTkCLHpfP9phSpe4BVvDR9pump</t>
+          <t>F3DkNMXQ4pJAXuut5WsESKAyPJRB8MnTsQ53pG8npump</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:19</t>
+          <t>2026-10-16 04:53:22</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:20</t>
+          <t>2026-10-16 04:53:23</t>
         </is>
       </c>
     </row>
@@ -2011,61 +2031,61 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Big Ugly Cucks</t>
+          <t>Tesla x SpaceX</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>BUC</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>+3.1%</t>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>+19.0%</t>
+          <t>+11.3%</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>1.03090547</v>
+        <v>0.938038267</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>0.03090546999999999</v>
+        <v>-0.06196173299999996</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 3.1% (-13.4% from peak, tol=10%)</t>
+          <t>trade-event breakeven -6.2%</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>JANiakLq3CbkQmmkVsnwrExwEvonYN2x1tZySUtzpump</t>
+          <t>Hj5Ffdunco3i5Vk8tDvcwF4BhhFvCcdBx9bbeTUFpump</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:23</t>
+          <t>2026-10-16 04:54:07</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:47</t>
+          <t>2026-10-16 04:54:08</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2095,12 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Big Ugly Cucks</t>
+          <t>Tesla Roadster</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>BUC</t>
+          <t>Roadster</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -2090,12 +2110,12 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>+99.2%</t>
+          <t>+49.4%</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>+157.9%</t>
+          <t>+93.3%</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2107,29 +2127,29 @@
         <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>1.991922249</v>
+        <v>1.494056798</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>0.9919222489999999</v>
+        <v>0.4940567979999999</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 99.2% (locked +100%, peak +158%)</t>
+          <t>amm trailing-stop 50.9% (-21.9% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>J77Z9ACmdmKdNJ63LpufGqW8RpZyxh9jybPN5W9ypump</t>
+          <t>B5TLyxPwhiiihAcwZsaqYTsCaZjtZw22ep3sNBAkTccs</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:23:09</t>
+          <t>2026-10-16 04:54:16</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:23:16</t>
+          <t>2026-10-16 04:54:17</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2159,12 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>AutoCorp</t>
+          <t>Tesla Roadster</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>CORP</t>
+          <t>Roadster</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
@@ -2167,12 +2187,12 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>EkC97ruNmtDw9Rq3DPXTwhx6VhxTgrRH6m7XvsjAkKUM</t>
+          <t>Gca6rP2fRYUbPyG2mZuGT6tmtCQKFZNEfdeZ6Lzfpump</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 03:23:41</t>
+          <t>2026-10-16 04:54:18</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr"/>
@@ -2183,46 +2203,410 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>number go hmm</t>
+          <t>Wherewe'regoingwedontneedroads</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>PONDR</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
+          <t>Roads?</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>-4.1%</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>-4.1%</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>0.9593773370000001</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>-0.04062266299999995</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>trade-event stop-loss -4.1%</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>gqKw5LUXBi1fPWLfnaKQXMHV3KbfFNAdATuMzQDpump</t>
+        </is>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:36</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>BOTs</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>+267.8%</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>+479.0%</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>3.678348185</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>2.678348185</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>trade-event trailing-stop 267.8% (-36.5% from peak, tol=28%)</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>FR2kf3htna5puoSxAjPedG7rgTkxfXvZjrL8x4zQpump</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:44</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>PEPEDOG WIF SWORD</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>$PDWS</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>0.990009119</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>-0.009990881000000007</v>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>watchdog dead-coin 0.0% after 30s</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>8KTWPFaHyF5ytwGxgkzdFNAxZ3QqaCne9v4Njvwspump</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:46</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Runfolio</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>SRUN</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>-4.5%</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>-3.6%</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0.954591436</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>-0.04540856400000004</v>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>amm stop-loss -3.6%</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>DgbUaUULgviY2JPr8DGFJ42hg7NAQ6T7tjBu3DnHpump</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:59</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:54:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Upside Down Tesla Roadster</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>UDTR</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr"/>
+      <c r="J29" s="10" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>9EaQMq1EMbFZNHSdYwZuB5HCxEqfX6Dca2uSKhWnpump</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 03:23:59</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>8V5cBBDmdVZqhCq6VX1MXJqJ2XV9NpnYDRJTsYa7pump</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:05</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Runfolio</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>SRUN</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>+27.4%</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>+61.7%</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>1.27383053</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>0.2738305299999999</v>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>watchdog trailing-stop 27.4% (-21.2% from peak, tol=18%)</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>CGh5gMJUAuNL4EuJRbi1f1ZL18pktxgaWcZT3DmCpump</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:33</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Tom Holland Stare</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>STARE</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>holding</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>4G7RSiTHThwa6BP2Z8K2186BpaHU4w6bCggrZp14pump</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:47</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N25"/>
+  <autoFilter ref="A1:N31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2233,7 +2617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2291,161 +2675,161 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:08</t>
+          <t>2026-10-16 04:50:34</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>50 Scent</t>
+          <t>Flying Tesla Roadster 2.0</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>50 Scent</t>
+          <t>FTR2,0</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>80.87747102079877</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>0</v>
+        <v>521.0370369380399</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=27 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 80.88% | 2- Total Locked Liquidity $521 | BLOCK insider-whale 151,660,777 tokens (&gt;= 100,000,000)</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0</v>
+        <v>151660777.334045</v>
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>29LArDCs37HMj3fgy7rh2xc9qUkc885QYNUykLAgpump</t>
+          <t>7WZMwGsTkRkGyHHcAyCA1bcS65eaAQrFMakUc1LVz6pE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:50</t>
+          <t>2026-10-16 04:52:06</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Saindra</t>
+          <t>Hashlings</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>SAINDRA</t>
+          <t>HASHLINGS</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>50.52363835772071</v>
+        <v>135.291892573446</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>1821.64592557876</v>
+        <v>0</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 50.52% | 2- Total Locked Liquidity $1.8K | BLOCK insider-whale 126,235,294 tokens (&gt;= 100,000,000); sniper-bundle 10 wallets besides LP</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=16 &gt; 5</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
-        <v>126235294.117647</v>
+        <v>0</v>
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>7bQwGYwJzwcegyt8Ejyobu39BYLg5xFNuJka15Qypump</t>
+          <t>CCUBjGRFFYJvqYvPyL5YuZjCnigCVAsoszCN1efpump</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:54</t>
+          <t>2026-10-16 04:52:29</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Doge4Goat</t>
+          <t>Up Side Down Tesla</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Doge4Goat</t>
+          <t>USDT</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>54.83302030941268</v>
+        <v>135.291892573446</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>1583.46437885452</v>
+        <v>0</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 54.83% | 2- Total Locked Liquidity $1.6K | BLOCK sniper-bundle 19 wallets besides LP</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK clone-ticker USDT</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>68971002.17336901</v>
+        <v>0</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>6nsnpCggMD3CPSstZXKCiFPTdRx72JZZzxyCz3prpump</t>
+          <t>6WpqXNcoiXPV46yGrVDrYRAGxD7FJEYQ9BEqb1dopump</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:20:55</t>
+          <t>2026-10-16 04:55:20</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>CLAU</t>
+          <t>ROADSTER</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>CLAU</t>
+          <t>ROADSTER</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>99.53393542612206</v>
+        <v>135.291892573446</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>10.92207442124</v>
+        <v>0</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 99.53% | 2- Total Locked Liquidity $11 | BLOCK sniper-bundle 14 wallets besides LP</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=39 &gt; 5</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
-        <v>32712312.494382</v>
+        <v>0</v>
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>6iq5aCmEFh96XZswHgzivLn1XN4Y8N7aFioAGyMPpump</t>
+          <t>Co7ASA9DUnXSWrkS1wNirtAPDrPP9rVg389wnHLhX2v6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 03:22:22</t>
+          <t>2026-10-16 04:55:32</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>Afia Birago Frog</t>
+          <t xml:space="preserve">2026 Tesla Roadster </t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Afia</t>
+          <t>Roadster</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -2456,7 +2840,7 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=37 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=28 &gt; 5</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
@@ -2464,7 +2848,43 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>JNgK7oNeuJWS14Wxoj5MwPfGDiLK8zCL9jm2orcgrAS</t>
+          <t>H6BE9eYY95THhHa2BJJw8pjdzHyNqCJ8DtnE24cspump</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:55:41</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>TESLA ROADSTER</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>ROADSTER</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>135.291892573446</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=40 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>7hW6GFdvuQNvajVd6oy8K6UKP1NLfJB98S6unvuV9zFe</t>
         </is>
       </c>
     </row>

--- a/reports/pumpfun_trades_live.xlsx
+++ b/reports/pumpfun_trades_live.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Blocked" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trades'!$A$1:$N$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +45,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -138,9 +138,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -670,7 +670,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>+63.0%</t>
+          <t>+55.5%</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>28.080913787</v>
+        <v>24.150907264</v>
       </c>
     </row>
     <row r="21">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>6.080913787</v>
+        <v>4.150907264000001</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -851,63 +851,43 @@
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Roadster Wif Wings</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>OKAY</t>
+          <t>RWW</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>+76.9%</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr"/>
       <c r="H2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="12" t="n">
-        <v>0.958761799</v>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>-0.04123820099999997</v>
-      </c>
+      <c r="I2" s="10" t="inlineStr"/>
+      <c r="J2" s="10" t="inlineStr"/>
       <c r="K2" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -4.1%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>GHnGviuMzqMoBx8NuZNN3X5QDkYA7mZBu3xVGoPNmVzT</t>
+          <t>6oJLFN6wVz562HyB3LJHHxa2cG3fPr1DhBpD1gJ9pump</t>
         </is>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:24</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:50:25</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:57:40</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="n">
@@ -915,12 +895,12 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Flying Tesla Roadster 2.0</t>
+          <t>Crashed Tesla Roadster</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>FTR</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -930,7 +910,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>+24.4%</t>
+          <t>+2.5%</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -947,29 +927,29 @@
         <v>1</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>1.244047792</v>
+        <v>1.025194494</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>0.2440477919999999</v>
+        <v>0.02519449399999996</v>
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>trade-event ratchet-floor 24.4% (locked +25%, peak +68%)</t>
+          <t>trade-event ratchet-floor 2.5% (locked +25%, peak +69%)</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
         <is>
-          <t>J5s6eTHv3ZhzG5X4LrEwbr1LgRoj5tSmsZDrxntMpump</t>
+          <t>5VtDTJVXmbGZFuWtY8R1hmQ7nHpTLXuYDrqGzLXdbtf1</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:29</t>
+          <t>2026-10-16 04:57:54</t>
         </is>
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:31</t>
+          <t>2026-10-16 04:57:56</t>
         </is>
       </c>
     </row>
@@ -979,12 +959,12 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>numen.cash</t>
+          <t>PumpFun’s Cat</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>NUMEN</t>
+          <t>Primo</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -994,12 +974,12 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>+56.8%</t>
+          <t>+81.1%</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>+97.7%</t>
+          <t>+158.6%</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -1011,29 +991,29 @@
         <v>1</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1.568295652</v>
+        <v>1.810735202</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>0.568295652</v>
+        <v>0.810735202</v>
       </c>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>watchdog trailing-stop 56.8% (-20.7% from peak, tol=18%)</t>
+          <t>trade-event ratchet-floor 81.1% (locked +100%, peak +159%)</t>
         </is>
       </c>
       <c r="L4" s="10" t="inlineStr">
         <is>
-          <t>GvEjB2Z24Hbq3Tf3F5e5vPgBpmV5p7YnL4SLDpoapump</t>
+          <t>94npHuXhjFYj2fTdiip6quMQrBhJzudUSCGR3puepump</t>
         </is>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:31</t>
+          <t>2026-10-16 04:58:03</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:47</t>
+          <t>2026-10-16 04:58:03</t>
         </is>
       </c>
     </row>
@@ -1043,43 +1023,63 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>p-null.si</t>
+          <t>WRECKED  Tesla Roadster</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>p(null)</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
+          <t>WTR</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>+20.6%</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>+53.3%</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="inlineStr"/>
-      <c r="J5" s="10" t="inlineStr"/>
+      <c r="I5" s="12" t="n">
+        <v>1.206288342</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0.2062883419999999</v>
+      </c>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event ratchet-floor 20.6% (locked +25%, peak +53%)</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>DuQU1Fi4KmT4cQgn1k1QYkqtYVEMRhEXbdijsipypump</t>
+          <t>33uN8Mr6DYSUQ4yPdqwjDTmufBuPbrRJfZnPuC4n71gh</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:37</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:58:04</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:58:06</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -1087,20 +1087,20 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Cuck Coding</t>
+          <t>CRASHED TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Cuck</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
+      <c r="E6" s="11" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="9" t="inlineStr"/>
       <c r="H6" s="12" t="n">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>4RrzBXWpbXbSsTNHxDxEjffrSzuG4HPoSLwPr7yVpump</t>
+          <t>7YX7sTVP8nvdTQnhpZUCXTfE1F9Cxmt74AaaMNXMpump</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:41</t>
+          <t>2026-10-16 04:58:21</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr"/>
@@ -1131,61 +1131,61 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Carcoin</t>
+          <t>oneseat</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Car</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>+18.5%</t>
+          <t>oneseat</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>+44.3%</t>
+          <t>+19.1%</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>1.184982451</v>
+        <v>0.973816386</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>0.184982451</v>
+        <v>-0.02618361400000002</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 18.5% (-17.9% from peak, tol=10%)</t>
+          <t>watchdog breakeven -2.6%</t>
         </is>
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>E8W7MLBp7anWDj1zS5FCtF4Xb2nehzT8ze7UDd91pump</t>
+          <t>F2nVtaA1StAqRSYjiMYLXZsRuiCTCRK4RTL1tv1cpump</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:42</t>
+          <t>2026-10-16 04:58:34</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:43</t>
+          <t>2026-10-16 04:58:34</t>
         </is>
       </c>
     </row>
@@ -1195,61 +1195,61 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Flying Tesla Roadster 2.0</t>
+          <t>CRASHED TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>FTR2</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>-7.5%</t>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>+71.8%</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
+          <t>+147.4%</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>-7.5%</t>
-        </is>
-      </c>
       <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.9245233430000001</v>
+        <v>1.717512126</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>-0.07547665699999995</v>
+        <v>0.7175121259999999</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>trade-event stop-loss -7.5%</t>
+          <t>watchdog trailing-stop 71.8% (-30.6% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>Ex8ZXJUp2WbmHJXmA1TfJkL8RVngbHBqTD7JDz1Xpump</t>
+          <t>9MuwhR7VTDbnUHHGG6YquTdDUQhKAFFami52uEhipump</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:09</t>
+          <t>2026-10-16 04:58:40</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:10</t>
+          <t>2026-10-16 04:58:41</t>
         </is>
       </c>
     </row>
@@ -1259,61 +1259,61 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>I Wish Tech Wasn't Here</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>IWTH</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+          <t>CHC</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>LOST</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>-7.6%</t>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>+32.9%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.924192439</v>
+        <v>0.9490407239999999</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>-0.07580756099999997</v>
+        <v>-0.05095927600000005</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>watchdog breakeven -7.6%</t>
+          <t>watchdog breakeven -5.1%</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr">
         <is>
-          <t>FdnSb7PCMQTfJ1T2335YYdTyGrJhtKx79X9pgLRUpump</t>
+          <t>8HufGjaY4eh3L6tN2JMUGMaBJQXtsSyrp9UypEPxpump</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:31</t>
+          <t>2026-10-16 04:58:51</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:32</t>
+          <t>2026-10-16 04:58:52</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Tesla x SpaceX</t>
+          <t>PARTICIPATE</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>TESLAXSPX</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -1338,46 +1338,46 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>+8.5%</t>
+          <t>+35.9%</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>1.073717595</v>
+        <v>1.05455142</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>0.07371759499999997</v>
+        <v>0.05455141999999991</v>
       </c>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 8.5% after 30s</t>
+          <t>watchdog trailing-stop 5.5% (-22.4% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>CdpmUkhuiCArgH7LUUWVjU8LoQV3iZiYLpDAY79JxkiC</t>
+          <t>XW66DrjnTUK3CU7pCMkALWniQDL9Bj2cbxeT4Wmpump</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:40</t>
+          <t>2026-10-16 04:58:55</t>
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:11</t>
+          <t>2026-10-16 04:58:56</t>
         </is>
       </c>
     </row>
@@ -1387,61 +1387,61 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>gently used  tesla roadster</t>
+          <t>CRASHING TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>UTR</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>+2.8%</t>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>+24.5%</t>
+          <t>+10.9%</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1.028018102</v>
+        <v>0.9730908</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>0.0280181020000001</v>
+        <v>-0.02690919999999997</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 2.8% (-17.4% from peak, tol=10%)</t>
+          <t>trade-event breakeven -2.7%</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>J6pEUdFLH72dAjLwxyc5Gjn9ukF6ERc6zpFSwdNTpump</t>
+          <t>c5U8cmrMSqwR21SB4GPvzqgbvGh4fsCaXUXXBFvpump</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:48</t>
+          <t>2026-10-16 04:58:59</t>
         </is>
       </c>
       <c r="N11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:51:49</t>
+          <t>2026-10-16 04:59:00</t>
         </is>
       </c>
     </row>
@@ -1451,43 +1451,63 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Flying Tesla Roadster</t>
+          <t>COORDINATE</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>FTR</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
+          <t>CRD</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>+1.9%</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
+      <c r="I12" s="12" t="n">
+        <v>1.018744421</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>0.01874442100000007</v>
+      </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog dead-coin 2.9% after 30s</t>
         </is>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>XUWauZnrx6oHSQyQosg88jwnM3gdVFqH4UZyjWDpump</t>
+          <t>y2fXg3cza28zi4D6UZy7xsiFRMuCPSLADhS6eZopump</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:00</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:59:01</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:59:31</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -1495,63 +1515,43 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>AgentPlay</t>
+          <t>TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>AGENTPLAY</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>+35.1%</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>+70.8%</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>ROADSTER</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>1.350549879</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>0.3505498789999999</v>
-      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 35.1% (-20.9% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>ufPxxVUMKC1if3JFYuWSDiMSGbJtq9yRGVdprZUpump</t>
+          <t>HK5mbgqisnrh1JxsRnUQiisqrjgtQjeGCQsE4xTduT7s</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:12</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:52:13</t>
-        </is>
-      </c>
+          <t>2026-10-16 04:59:05</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -1559,20 +1559,20 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>grokazon</t>
+          <t>Neoncoin</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>grokazon</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+          <t>Neon</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr"/>
+      <c r="E14" s="11" t="inlineStr"/>
       <c r="F14" s="9" t="inlineStr"/>
       <c r="G14" s="9" t="inlineStr"/>
       <c r="H14" s="12" t="n">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>Ch7gZZqhZRnHnLJJsdpypNghGn3fDjuxQtr5qeWPpump</t>
+          <t>G5gqYSmC57waQQPBKFeEZCNhK5vbN7AmYCjfLMVpump</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:15</t>
+          <t>2026-10-16 04:59:11</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr"/>
@@ -1603,61 +1603,61 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Exploding Tesla Roadster</t>
+          <t>Floating Tesla Roadster</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>ETR</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>-4.4%</t>
+          <t>FTR</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>+87.7%</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+140.5%</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="H15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.956004272</v>
+        <v>1.877233731</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>-0.04399572799999996</v>
+        <v>0.877233731</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>trade-event stop-loss -4.4%</t>
+          <t>trade-event trailing-stop 87.7% (-21.9% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>DLP9o7efJKwJfX5QJ9FDGYohoCj3s6v99QkLKzeYpump</t>
+          <t>GTXAgEDXPAsawpsJY8x7gCQHLfsEgeukZm3SoFrepump</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:54</t>
+          <t>2026-10-16 04:59:16</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:54</t>
+          <t>2026-10-16 04:59:20</t>
         </is>
       </c>
     </row>
@@ -1667,43 +1667,63 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Sucking Tesla Roadster</t>
+          <t>Retroification</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="9" t="inlineStr"/>
-      <c r="G16" s="9" t="inlineStr"/>
+          <t>Retro</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>+31.0%</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>+76.2%</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
+      <c r="I16" s="12" t="n">
+        <v>1.309777158</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.3097771579999999</v>
+      </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>trade-event trailing-stop 31.0% (-25.7% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>AHnrPnY2pt7TCHXCS6CVd8d5pze4Nn59e16tJDYHpump</t>
+          <t>9cjErfLmhiFM495nnMM5JVbyZ2UffgLfdQdK3gNEpump</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:59</t>
-        </is>
-      </c>
-      <c r="N16" s="10" t="inlineStr"/>
+          <t>2026-10-16 04:59:28</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:59:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -1711,61 +1731,61 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Slighty Used Tesla Roadstar</t>
+          <t>Hunter Kiler</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Roadstar</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>+8.4%</t>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="H17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>1.084297394</v>
+        <v>0.924410463</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>0.08429739400000003</v>
+        <v>-0.07558953700000004</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 9.5% after 30s</t>
+          <t>watchdog stop-loss -7.6%</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>5psJDSu949XhzPQdfsvoGvF5kbLC3TjsQWpMdSw1pump</t>
+          <t>2hz6HprLfhiqTSEvUmSTyyYiJdUESjpUmwrhkUuApump</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:06</t>
+          <t>2026-10-16 04:59:30</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:36</t>
+          <t>2026-10-16 04:59:30</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1795,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Tesla Roadster</t>
+          <t>Retroification</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>Retro</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -1790,12 +1810,12 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>+17.7%</t>
+          <t>+11.4%</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>+40.3%</t>
+          <t>+78.0%</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1807,29 +1827,29 @@
         <v>1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1.17672305</v>
+        <v>1.114330494</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>0.1767230500000001</v>
+        <v>0.1143304940000001</v>
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 17.7% (-16.1% from peak, tol=10%)</t>
+          <t>trade-event ratchet-floor 11.4% (locked +25%, peak +78%)</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>18vuF9YNerpXUcSKBMLH7nqmxAiwe6FJCxRJeAopump</t>
+          <t>6vz8boZdaLV4tyk3fMRgVKzaMeKndDvm1p47z5VTpump</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:09</t>
+          <t>2026-10-16 04:59:57</t>
         </is>
       </c>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:12</t>
+          <t>2026-10-16 04:59:58</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1859,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Claudia's Cat Clay</t>
+          <t>Retroification</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>Retro</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -1854,12 +1874,12 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>+32.7%</t>
+          <t>+27.9%</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>+76.3%</t>
+          <t>+45.1%</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1871,29 +1891,29 @@
         <v>1</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1.326804239</v>
+        <v>1.279015944</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>0.3268042390000001</v>
+        <v>0.279015944</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 32.7% (-24.8% from peak, tol=18%)</t>
+          <t>watchdog trailing-stop 27.9% (-11.8% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>HLLwUbjfueZo1jw5fSML6MDbg9YzbCPGT8qcjJjfpump</t>
+          <t>6hihWrmFdYkTZYtxmSuft8yLmmNWLBKG91btqkZ4pump</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:15</t>
+          <t>2026-10-16 05:00:01</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:16</t>
+          <t>2026-10-16 05:00:04</t>
         </is>
       </c>
     </row>
@@ -1903,61 +1923,61 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Underrated Profit Simulator</t>
+          <t>Tesla Roadster</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>+70.3%</t>
+          <t>Roadster</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>+108.0%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>1.70306778</v>
+        <v>0.967949866</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>0.70306778</v>
+        <v>-0.03205013400000001</v>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 70.3% (-18.1% from peak, tol=18%)</t>
+          <t>watchdog dead-coin -2.2% after 30s</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>E9Xiz6zzpiBsMDkMMpHjnb2bfxvZWAKK1vk4cpV6pump</t>
+          <t>6HWCDcWgBArNJh5t8zZt48KTfx6gRhYuEtkaem5A4hv</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:21</t>
+          <t>2026-10-16 05:00:06</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:35</t>
+          <t>2026-10-16 05:00:36</t>
         </is>
       </c>
     </row>
@@ -1967,61 +1987,61 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Tesla Roadster</t>
+          <t>DVDification</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Roadster</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>+28.9%</t>
+          <t>DVD</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>LOST</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>+82.6%</t>
+          <t>+10.9%</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>1.288676328</v>
+        <v>0.955879909</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>0.288676328</v>
+        <v>-0.04412009100000003</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 28.9% (-29.4% from peak, tol=18%)</t>
+          <t>watchdog breakeven -4.4%</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>F3DkNMXQ4pJAXuut5WsESKAyPJRB8MnTsQ53pG8npump</t>
+          <t>4ghVLfouq1Z8z9LgpeT5m5qXXWMnoGB4TLsRxVjWpump</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:22</t>
+          <t>2026-10-16 05:00:11</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:53:23</t>
+          <t>2026-10-16 05:00:17</t>
         </is>
       </c>
     </row>
@@ -2031,61 +2051,61 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Tesla x SpaceX</t>
+          <t>Orbiting Tesla Roadster</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>-6.2%</t>
+          <t>OTR</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>+37.7%</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>+11.3%</t>
+          <t>+69.8%</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>+0.0%</t>
         </is>
       </c>
       <c r="H22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.938038267</v>
+        <v>1.377026275</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>-0.06196173299999996</v>
+        <v>0.377026275</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>trade-event breakeven -6.2%</t>
+          <t>trade-event trailing-stop 37.7% (-18.9% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>Hj5Ffdunco3i5Vk8tDvcwF4BhhFvCcdBx9bbeTUFpump</t>
+          <t>6y3VKHiHfFNtSAA7YZ36L6o9swwexFu5T8zBHwfEpump</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:07</t>
+          <t>2026-10-16 05:00:18</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:08</t>
+          <t>2026-10-16 05:00:19</t>
         </is>
       </c>
     </row>
@@ -2095,63 +2115,43 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Tesla Roadster</t>
+          <t>X Corporation</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Roadster</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>+49.4%</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>+93.3%</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>1.494056798</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>0.4940567979999999</v>
-      </c>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>amm trailing-stop 50.9% (-21.9% from peak, tol=18%)</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>B5TLyxPwhiiihAcwZsaqYTsCaZjtZw22ep3sNBAkTccs</t>
+          <t>C1C4Ri3p5t18v7A2rkgB6i3LWWxnn1JN7fx8B3ogpump</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:16</t>
-        </is>
-      </c>
-      <c r="N23" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:54:17</t>
-        </is>
-      </c>
+          <t>2026-10-16 05:00:34</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -2159,43 +2159,63 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Tesla Roadster</t>
+          <t>Thruster Tesla Roadster</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Roadster</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr"/>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
+          <t>TTR</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>+16.6%</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>+53.0%</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
       <c r="H24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
+      <c r="I24" s="12" t="n">
+        <v>1.166230319</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>0.1662303190000001</v>
+      </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>holding</t>
+          <t>watchdog ratchet-floor 16.6% (locked +25%, peak +53%)</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>Gca6rP2fRYUbPyG2mZuGT6tmtCQKFZNEfdeZ6Lzfpump</t>
+          <t>jg7XDPAHNBwC8ji6KgMDML9hcgGPgGTCom5CGdUpump</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:18</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr"/>
+          <t>2026-10-16 05:00:36</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:00:36</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -2203,63 +2223,43 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Wherewe'regoingwedontneedroads</t>
+          <t>Ledger Opus</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Roads?</t>
+          <t>Ledger</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>-4.1%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>0.9593773370000001</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>-0.04062266299999995</v>
-      </c>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
       <c r="K25" s="10" t="inlineStr">
         <is>
-          <t>trade-event stop-loss -4.1%</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>gqKw5LUXBi1fPWLfnaKQXMHV3KbfFNAdATuMzQDpump</t>
+          <t>55i8jYsSZw6qfDvP3c32UuaecgbVUBP1afyzsr2cpump</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:36</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:54:36</t>
-        </is>
-      </c>
+          <t>2026-10-16 05:00:49</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="n">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>BOTs</t>
+          <t>dog in pain</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>BOT</t>
+          <t>dip</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>+267.8%</t>
+          <t>+36.2%</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>+479.0%</t>
+          <t>+90.3%</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2299,29 +2299,29 @@
         <v>1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>3.678348185</v>
+        <v>1.361941248</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>2.678348185</v>
+        <v>0.3619412479999999</v>
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>trade-event trailing-stop 267.8% (-36.5% from peak, tol=28%)</t>
+          <t>trade-event trailing-stop 36.2% (-28.4% from peak, tol=18%)</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>FR2kf3htna5puoSxAjPedG7rgTkxfXvZjrL8x4zQpump</t>
+          <t>HcCGno67KpvFp14Cv9AF4EyaixZwkqSHT8bTpNiWpump</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:44</t>
+          <t>2026-10-16 05:00:53</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:51</t>
+          <t>2026-10-16 05:00:55</t>
         </is>
       </c>
     </row>
@@ -2331,63 +2331,43 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>PEPEDOG WIF SWORD</t>
+          <t>Buckle Up</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>$PDWS</t>
+          <t>UP</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>-1.0%</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>0.990009119</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>-0.009990881000000007</v>
-      </c>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
       <c r="K27" s="10" t="inlineStr">
         <is>
-          <t>watchdog dead-coin 0.0% after 30s</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>8KTWPFaHyF5ytwGxgkzdFNAxZ3QqaCne9v4Njvwspump</t>
+          <t>HQCgn1r9CnWffXnuNLnFnjp45Tg6WZu58zdJL1FCpump</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:46</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:55:16</t>
-        </is>
-      </c>
+          <t>2026-10-16 05:00:56</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n">
@@ -2395,61 +2375,61 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Runfolio</t>
+          <t>Deppy</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>SRUN</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>LOST</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>-4.5%</t>
+          <t>DPLYR</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>+8.8%</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
+          <t>+35.1%</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>-3.6%</t>
-        </is>
-      </c>
       <c r="H28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0.954591436</v>
+        <v>1.088137942</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>-0.04540856400000004</v>
+        <v>0.08813794199999991</v>
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>amm stop-loss -3.6%</t>
+          <t>watchdog trailing-stop 8.8% (-19.5% from peak, tol=10%)</t>
         </is>
       </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
-          <t>DgbUaUULgviY2JPr8DGFJ42hg7NAQ6T7tjBu3DnHpump</t>
+          <t>6UyfhoMxN7oECWAjtTjJPg4j7btfSsJCFPDPdaTSpump</t>
         </is>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:59</t>
+          <t>2026-10-16 05:01:02</t>
         </is>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:54:59</t>
+          <t>2026-10-16 05:01:04</t>
         </is>
       </c>
     </row>
@@ -2459,20 +2439,20 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Upside Down Tesla Roadster</t>
+          <t>Buckle Up</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>UDTR</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
+          <t>Buckle</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
       <c r="F29" s="9" t="inlineStr"/>
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="12" t="n">
@@ -2487,126 +2467,18 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>8V5cBBDmdVZqhCq6VX1MXJqJ2XV9NpnYDRJTsYa7pump</t>
+          <t>9Nq9BJZKEgArenwV5rkTMwQ7udvDaZMvuJh8LzG9pump</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16 04:55:05</t>
+          <t>2026-10-16 05:01:12</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr"/>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Runfolio</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>SRUN</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>WON</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>+27.4%</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>+61.7%</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>1.27383053</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>0.2738305299999999</v>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>watchdog trailing-stop 27.4% (-21.2% from peak, tol=18%)</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>CGh5gMJUAuNL4EuJRbi1f1ZL18pktxgaWcZT3DmCpump</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:55:33</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:55:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>Tom Holland Stare</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>STARE</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>4G7RSiTHThwa6BP2Z8K2186BpaHU4w6bCggrZp14pump</t>
-        </is>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-16 04:55:47</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N31"/>
+  <autoFilter ref="A1:N29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2617,7 +2489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2675,53 +2547,53 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:50:34</t>
+          <t>2026-10-16 04:57:46</t>
         </is>
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Flying Tesla Roadster 2.0</t>
+          <t>Crashing Tesla Roadster</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>FTR2,0</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="D2" s="17" t="n">
-        <v>80.87747102079877</v>
+        <v>135.291892573446</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>521.0370369380399</v>
+        <v>0</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 80.88% | 2- Total Locked Liquidity $521 | BLOCK insider-whale 151,660,777 tokens (&gt;= 100,000,000)</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=41 &gt; 5</t>
         </is>
       </c>
       <c r="G2" s="18" t="n">
-        <v>151660777.334045</v>
+        <v>0</v>
       </c>
       <c r="H2" s="16" t="inlineStr">
         <is>
-          <t>7WZMwGsTkRkGyHHcAyCA1bcS65eaAQrFMakUc1LVz6pE</t>
+          <t>GNS1QtQ6Af34GXV7jpbaRw8qocRzQAqiVaDvTrdeGXsr</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:06</t>
+          <t>2026-10-16 04:57:48</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Hashlings</t>
+          <t>Tusla</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>HASHLINGS</t>
+          <t>TUSLA</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -2732,7 +2604,7 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=16 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=10 &gt; 5</t>
         </is>
       </c>
       <c r="G3" s="18" t="n">
@@ -2740,60 +2612,60 @@
       </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
-          <t>CCUBjGRFFYJvqYvPyL5YuZjCnigCVAsoszCN1efpump</t>
+          <t>GnHdHDdW6xaxRikhqUF6xPMfZAkwzABDHy1qcMdypump</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:52:29</t>
+          <t>2026-10-16 04:58:06</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Up Side Down Tesla</t>
+          <t>loop</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>USDT</t>
+          <t>LOOP</t>
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>135.291892573446</v>
+        <v>81.17280146376258</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0</v>
+        <v>511.01029236709</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK clone-ticker USDT</t>
+          <t>1- Liquidity (LP tokens) Locked 81.17% | 2- Total Locked Liquidity $511 | BLOCK serial-deployer launches=17 &gt; 5; sniper-bundle 13 wallets besides LP</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>0</v>
+        <v>77049809.179616</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>6WpqXNcoiXPV46yGrVDrYRAGxD7FJEYQ9BEqb1dopump</t>
+          <t>9d8ndjxHQhqPcdd2p2cuX6VoXF6reueunRJg69Yopump</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:55:20</t>
+          <t>2026-10-16 04:58:42</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>ROADSTER</t>
+          <t>CRASHING TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>ROADSTER</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -2804,7 +2676,7 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=39 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=42 &gt; 5</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
@@ -2812,24 +2684,24 @@
       </c>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>Co7ASA9DUnXSWrkS1wNirtAPDrPP9rVg389wnHLhX2v6</t>
+          <t>AApuvmzW9bJ7SHSzEjHvzstdr9QJLJ1nNN7a8DLeuuAv</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:55:32</t>
+          <t>2026-10-16 04:58:43</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026 Tesla Roadster </t>
+          <t>Tusla</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Roadster</t>
+          <t>TUSLA</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -2840,51 +2712,87 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=28 &gt; 5</t>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=11 &gt; 5; insider-whale 151,660,777 tokens (&gt;= 100,000,000); sniper-bundle 8 wallets besides LP</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>151660777.334045</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>H6BE9eYY95THhHa2BJJw8pjdzHyNqCJ8DtnE24cspump</t>
+          <t>99g4nKmdaksbDjK2HQ2x6nxup4GQ9SUtMnN1JRx9pump</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>2026-10-16 04:55:41</t>
+          <t>2026-10-16 04:58:44</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>TESLA ROADSTER</t>
+          <t>CRASHED TESLA ROADSTER</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>ROADSTER</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
+        <v>64.03115847948177</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>1144.97777758131</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 64.03% | 2- Total Locked Liquidity $1.1K | BLOCK insider-whale 223,687,296 tokens (&gt;= 100,000,000)</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>223687296.374334</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>7czPyq89FNCUuaVEfbRjdyGwEe3PCdA2j5wNcq15oRVh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 05:00:02</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>S&amp;X</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>S&amp;X</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
         <v>135.291892573446</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=40 &gt; 5</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="n">
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>1- Liquidity (LP tokens) Locked 135.29% | 2- Total Locked Liquidity $0 | BLOCK serial-deployer launches=8 &gt; 5</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>7hW6GFdvuQNvajVd6oy8K6UKP1NLfJB98S6unvuV9zFe</t>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>91x8EmndhRgwudV8zwQuhyK5XoLqUc4n1M5PMhyppump</t>
         </is>
       </c>
     </row>
